--- a/access_control_forms/002_smart_monitoring_access_request_form--access_control_forms.xlsx
+++ b/access_control_forms/002_smart_monitoring_access_request_form--access_control_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'monitoring_system',_'label':_'monitoring_system'}</t>
+          <t>monitoring_system</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Monitoring System', 'label': 'Monitoring System'}</t>
+          <t>Monitoring System</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'smart_monitoring_system',_'label':_'smart_monitoring_system'}</t>
+          <t>smart_monitoring_system</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Smart Monitoring System', 'label': 'Smart Monitoring System'}</t>
+          <t>Smart Monitoring System</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'read-only',_'label':_'read-only'}</t>
+          <t>read-only</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Read-Only', 'label': 'Read-Only'}</t>
+          <t>Read-Only</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'read/write',_'label':_'read/write'}</t>
+          <t>read/write</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Read/Write', 'label': 'Read/Write'}</t>
+          <t>Read/Write</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'one-off',_'label':_'one-off'}</t>
+          <t>one-off</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'One-off', 'label': 'One-off'}</t>
+          <t>One-off</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'recurring',_'label':_'recurring'}</t>
+          <t>recurring</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Recurring', 'label': 'Recurring'}</t>
+          <t>Recurring</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'days',_'label':_'days'}</t>
+          <t>days</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Days', 'label': 'Days'}</t>
+          <t>Days</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'weeks',_'label':_'weeks'}</t>
+          <t>weeks</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Weeks', 'label': 'Weeks'}</t>
+          <t>Weeks</t>
         </is>
       </c>
     </row>
